--- a/questionnaire_templates/034_mathematics_learning_difficulty_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/034_mathematics_learning_difficulty_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'k-5',_'value':_'k_5'}</t>
+          <t>k-5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'K-5', 'value': 'k_5'}</t>
+          <t>K-5</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'6-8',_'value':_'six_eight'}</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '6-8', 'value': 'six_eight'}</t>
+          <t>6-8</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'9-12',_'value':_'nine_twelve'}</t>
+          <t>9-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '9-12', 'value': 'nine_twelve'}</t>
+          <t>9-12</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'fractions',_'value':_'fractions'}</t>
+          <t>fractions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'fractions', 'value': 'fractions'}</t>
+          <t>fractions</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'algebra',_'value':_'algebra'}</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'algebra', 'value': 'algebra'}</t>
+          <t>algebra</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'geometry',_'value':_'geometry'}</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'geometry', 'value': 'geometry'}</t>
+          <t>geometry</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'easy',_'value':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'easy', 'value': 'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'medium', 'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'hard',_'value':_'hard'}</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'hard', 'value': 'hard'}</t>
+          <t>hard</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'tutor_help',_'value':_'tutor_help'}</t>
+          <t>tutor_help</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'tutor_help', 'value': 'tutor_help'}</t>
+          <t>tutor help</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'online_resources',_'value':_'online_resources'}</t>
+          <t>online_resources</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'online_resources', 'value': 'online_resources'}</t>
+          <t>online resources</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'practice_problems',_'value':_'practice_problems'}</t>
+          <t>practice_problems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'practice_problems', 'value': 'practice_problems'}</t>
+          <t>practice problems</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'homework_help',_'value':_'homework_help'}</t>
+          <t>homework_help</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'homework_help', 'value': 'homework_help'}</t>
+          <t>homework help</t>
         </is>
       </c>
     </row>
